--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484259_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484259_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5881</v>
+        <v>12.6263</v>
       </c>
       <c r="E2" t="n">
-        <v>12.4954</v>
+        <v>10.5337</v>
       </c>
       <c r="F2" t="n">
         <v>2.0926</v>
@@ -610,10 +610,10 @@
         <v>2.5395</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0733</v>
+        <v>1.1115</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0157</v>
+        <v>1.0539</v>
       </c>
       <c r="U2" t="n">
         <v>0.0576</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>G. PÉREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.904</v>
+        <v>2.7841</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0247</v>
+        <v>2.3508</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1207</v>
+        <v>0.4333</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0568</v>
+        <v>1.4963</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6516</v>
+        <v>1.5636</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4052</v>
+        <v>-0.0673</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4262</v>
+        <v>0.8471</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2113</v>
+        <v>0.779</v>
       </c>
       <c r="L3" t="n">
-        <v>1.215</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3694</v>
+        <v>0.6492</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4403</v>
+        <v>0.7846</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8097</v>
+        <v>-0.1354</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4969</v>
+        <v>0.0887</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4015</v>
+        <v>0.2581</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0954</v>
+        <v>-0.1694</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2186</v>
+        <v>0.2224</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.441</v>
       </c>
       <c r="X3" t="n">
         <v>-1.2186</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MASLLORENS MANRIQUE</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8591</v>
+        <v>2.0385</v>
       </c>
       <c r="E4" t="n">
-        <v>1.127</v>
+        <v>2.1863</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7322</v>
+        <v>-0.1479</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3318</v>
+        <v>2.0568</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1312</v>
+        <v>1.6516</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2005</v>
+        <v>0.4052</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3978</v>
+        <v>2.4262</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2635</v>
+        <v>1.2113</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6613</v>
+        <v>1.215</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9340000000000001</v>
+        <v>-0.3694</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3948</v>
+        <v>0.4403</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5393</v>
+        <v>-0.8097</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3553</v>
+        <v>-0.3625</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9245</v>
+        <v>-0.2399</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4308</v>
+        <v>-0.1226</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2186</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>A. MASLLORENS MANRIQUE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4655</v>
+        <v>1.4063</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4408</v>
+        <v>0.783</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0248</v>
+        <v>0.6232</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4963</v>
+        <v>1.3318</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5636</v>
+        <v>0.1312</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0673</v>
+        <v>1.2005</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8471</v>
+        <v>0.3978</v>
       </c>
       <c r="K5" t="n">
-        <v>0.779</v>
+        <v>-0.2635</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.6613</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6492</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7846</v>
+        <v>0.3948</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1354</v>
+        <v>0.5393</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2299</v>
+        <v>0.9024</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.652</v>
+        <v>0.5806</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5779</v>
+        <v>0.3218</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2224</v>
+        <v>-1.2186</v>
       </c>
       <c r="W5" t="n">
-        <v>1.441</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>-1.2186</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5203</v>
+        <v>0.9326</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0683</v>
+        <v>0.2351</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5886</v>
+        <v>0.6976</v>
       </c>
       <c r="G6" t="n">
         <v>0.8209</v>
@@ -922,13 +922,13 @@
         <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4996</v>
+        <v>-0.0873</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3026</v>
+        <v>0.0007</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.197</v>
+        <v>-0.0881</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3869</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4426</v>
+        <v>0.0708</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0218</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5793</v>
+        <v>0.6882</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1383</v>
@@ -1000,13 +1000,13 @@
         <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4996</v>
+        <v>0.0138</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5309</v>
+        <v>-0.1265</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0313</v>
+        <v>0.1402</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7153</v>
+        <v>-1.147</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5733</v>
+        <v>-0.9778</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.142</v>
+        <v>-0.1692</v>
       </c>
       <c r="G8" t="n">
         <v>0.3981</v>
@@ -1078,13 +1078,13 @@
         <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.4196</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5147</v>
+        <v>0.1102</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3366</v>
+        <v>0.3094</v>
       </c>
       <c r="V8" t="n">
         <v>-2.16</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8216</v>
+        <v>-1.4033</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8807</v>
+        <v>-2.5169</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0591</v>
+        <v>1.1136</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8083</v>
@@ -1156,13 +1156,13 @@
         <v>1.9534</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3957</v>
+        <v>0.0226</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4153</v>
+        <v>-0.0514</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0196</v>
+        <v>0.0741</v>
       </c>
       <c r="V9" t="n">
         <v>0.5545</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.205</v>
+        <v>-2.2945</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5871</v>
+        <v>-2.4859</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3821</v>
+        <v>0.1914</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3824</v>
@@ -1234,13 +1234,13 @@
         <v>0.3907</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0407</v>
+        <v>-0.0488</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3026</v>
+        <v>-0.2015</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3433</v>
+        <v>0.1527</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2772</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6465</v>
+        <v>-2.3316</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8033</v>
+        <v>-2.2977</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1568</v>
+        <v>-0.0338</v>
       </c>
       <c r="G11" t="n">
         <v>1.024</v>
@@ -1312,13 +1312,13 @@
         <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7202</v>
+        <v>1.0351</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0221</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.5074</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4373</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0858</v>
+        <v>-3.0059</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6472</v>
+        <v>-2.4855</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4386</v>
+        <v>-0.5203</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5312</v>
@@ -1390,13 +1390,13 @@
         <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2774</v>
+        <v>-0.1974</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4237</v>
+        <v>-0.262</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1463</v>
+        <v>0.0646</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8865</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4786</v>
+        <v>-3.432</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3437</v>
+        <v>-2.2426</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1349</v>
+        <v>-1.1894</v>
       </c>
       <c r="G13" t="n">
         <v>-1.0556</v>
@@ -1468,13 +1468,13 @@
         <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4545</v>
+        <v>-0.4079</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1816</v>
+        <v>-0.0805</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.273</v>
+        <v>-0.3275</v>
       </c>
       <c r="V13" t="n">
         <v>-1.7731</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.941600000000001</v>
+        <v>6.244299999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.162499999999998</v>
+        <v>2.4651</v>
       </c>
       <c r="F14" t="n">
         <v>3.7793</v>
@@ -1516,13 +1516,13 @@
         <v>13.8556</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6711999999999998</v>
+        <v>-0.6712000000000007</v>
       </c>
       <c r="J14" t="n">
         <v>11.0363</v>
       </c>
       <c r="K14" t="n">
-        <v>9.006200000000003</v>
+        <v>9.006200000000002</v>
       </c>
       <c r="L14" t="n">
         <v>2.0301</v>
@@ -1546,13 +1546,13 @@
         <v>13.6741</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1872</v>
+        <v>2.4898</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2668</v>
+        <v>1.5694</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9203000000000002</v>
+        <v>0.9202</v>
       </c>
       <c r="V14" t="n">
         <v>-7.476100000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0702</v>
+        <v>2.7003</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6159</v>
+        <v>1.9192</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4543</v>
+        <v>0.7811</v>
       </c>
       <c r="G15" t="n">
         <v>0.067</v>
@@ -1624,13 +1624,13 @@
         <v>2.7348</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0201</v>
+        <v>-0.39</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2529</v>
+        <v>0.0504</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7672</v>
+        <v>-0.4404</v>
       </c>
       <c r="V15" t="n">
         <v>2.4373</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5656</v>
+        <v>0.7712</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6566</v>
+        <v>-0.9338</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2222</v>
+        <v>1.7051</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.484</v>
+        <v>1.6052</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8921</v>
+        <v>0.9992</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.592</v>
+        <v>0.606</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.7146</v>
+        <v>2.1095</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5283</v>
+        <v>1.9071</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.1863</v>
+        <v>0.2023</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7694</v>
+        <v>-0.5042</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3638</v>
+        <v>-0.9079</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4056</v>
+        <v>0.4037</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7581</v>
+        <v>0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7348</v>
+        <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6274</v>
+        <v>-0.52</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0347</v>
+        <v>-0.5624</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4074</v>
+        <v>0.0425</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6642</v>
+        <v>-0.5094</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6642</v>
+        <v>-0.1773</v>
       </c>
     </row>
     <row r="17">
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0025</v>
+        <v>-0.0814</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5405</v>
+        <v>1.2873</v>
       </c>
       <c r="F18" t="n">
-        <v>1.543</v>
+        <v>-1.3687</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6052</v>
+        <v>-2.1981</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9992</v>
+        <v>-2.2512</v>
       </c>
       <c r="I18" t="n">
-        <v>0.606</v>
+        <v>0.0531</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1095</v>
+        <v>0.1988</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9071</v>
+        <v>-0.5296</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2023</v>
+        <v>0.7284</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5042</v>
+        <v>-2.3969</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9079</v>
+        <v>-1.7217</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4037</v>
+        <v>-0.6753</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1488</v>
+        <v>-3.1255</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2887</v>
+        <v>-0.3535</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1691</v>
+        <v>-0.2736</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1196</v>
+        <v>-0.0799</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5094</v>
+        <v>4.033</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3321</v>
+        <v>4.4876</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1773</v>
+        <v>-0.4545</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6595</v>
+        <v>-0.2096</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6806</v>
+        <v>-2.5666</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3401</v>
+        <v>2.357</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1981</v>
+        <v>-2.484</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.2512</v>
+        <v>-0.8921</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0531</v>
+        <v>-1.592</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1988</v>
+        <v>-1.7146</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5296</v>
+        <v>-0.5283</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7284</v>
+        <v>-1.1863</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3969</v>
+        <v>-0.7694</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7217</v>
+        <v>-0.3638</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6753</v>
+        <v>-0.4056</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1255</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5627</v>
+        <v>2.7348</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9316</v>
+        <v>-0.1479</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8803</v>
+        <v>0.1247</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0513</v>
+        <v>-0.2726</v>
       </c>
       <c r="V19" t="n">
-        <v>4.033</v>
+        <v>0.6642</v>
       </c>
       <c r="W19" t="n">
-        <v>4.4876</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4545</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9114</v>
+        <v>-0.6836</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0455</v>
+        <v>0.1438</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8659</v>
+        <v>-0.8274</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1937</v>
+        <v>-1.8363</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6526</v>
+        <v>-1.7153</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4589</v>
+        <v>-0.121</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1186</v>
+        <v>-1.1373</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.7128</v>
+        <v>-1.0169</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5942</v>
+        <v>-0.1204</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0751</v>
+        <v>-0.699</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0601</v>
+        <v>-0.6984</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1352</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3559</v>
+        <v>-0.3514</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2685</v>
+        <v>-0.1794</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08740000000000001</v>
+        <v>-0.1721</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.0503</v>
+        <v>0.3321</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.0503</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1075</v>
+        <v>-0.9738</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3618</v>
+        <v>0.324</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7457</v>
+        <v>-1.2978</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8363</v>
+        <v>-2.0508</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7153</v>
+        <v>-1.9153</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.121</v>
+        <v>-0.1354</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1373</v>
+        <v>-0.6127</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0169</v>
+        <v>-0.6127</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1204</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.699</v>
+        <v>-1.438</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6984</v>
+        <v>-1.3026</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.1354</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7753</v>
+        <v>-0.7277</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6849</v>
+        <v>-0.282</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.4458</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3321</v>
+        <v>1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>2.4373</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1346</v>
+        <v>-1.3811</v>
       </c>
       <c r="E22" t="n">
         <v>-1.355</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2204</v>
+        <v>-0.0261</v>
       </c>
       <c r="G22" t="n">
         <v>-2.372</v>
@@ -2170,13 +2170,13 @@
         <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4583</v>
+        <v>0.2118</v>
       </c>
       <c r="T22" t="n">
         <v>-0.22</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6783</v>
+        <v>0.4318</v>
       </c>
       <c r="V22" t="n">
         <v>2.5372</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1761</v>
+        <v>-1.4364</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1217</v>
+        <v>-0.6522</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2978</v>
+        <v>-0.7842</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0508</v>
+        <v>-1.1937</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9153</v>
+        <v>-1.6526</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1354</v>
+        <v>0.4589</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6127</v>
+        <v>-1.1186</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6127</v>
+        <v>-1.7128</v>
       </c>
       <c r="L23" t="n">
+        <v>0.5942</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.0751</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.0601</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.1352</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.8309</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.6618000000000001</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-2.0503</v>
+      </c>
+      <c r="W23" t="n">
         <v>0</v>
       </c>
-      <c r="M23" t="n">
-        <v>-1.438</v>
-      </c>
-      <c r="N23" t="n">
-        <v>-1.3026</v>
-      </c>
-      <c r="O23" t="n">
-        <v>-0.1354</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="S23" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="T23" t="n">
-        <v>-0.4842</v>
-      </c>
-      <c r="U23" t="n">
-        <v>-0.4458</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.2186</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.2186</v>
-      </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.0503</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3401</v>
+        <v>-2.0128</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0764</v>
+        <v>-0.8853</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2637</v>
+        <v>-1.1275</v>
       </c>
       <c r="G24" t="n">
         <v>-1.2619</v>
@@ -2326,13 +2326,13 @@
         <v>0.1953</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.2078</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9988</v>
+        <v>0.1899</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1183</v>
+        <v>0.0178</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1773</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.7319</v>
+        <v>-2.4415</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3674</v>
+        <v>-0.2663</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3645</v>
+        <v>-2.1752</v>
       </c>
       <c r="G25" t="n">
         <v>-0.9816</v>
@@ -2404,13 +2404,13 @@
         <v>0.1953</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5497</v>
+        <v>-0.2593</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3494</v>
+        <v>-0.2482</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2004</v>
+        <v>-0.0111</v>
       </c>
       <c r="V25" t="n">
         <v>-1.3959</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.9417</v>
+        <v>-5.2676</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.7793</v>
+        <v>-3.7792</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.162400000000001</v>
+        <v>-1.4883</v>
       </c>
       <c r="G26" t="n">
         <v>-13.1843</v>
@@ -2452,7 +2452,7 @@
         <v>-13.8555</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6710999999999999</v>
+        <v>0.6710999999999997</v>
       </c>
       <c r="J26" t="n">
         <v>-2.148</v>
@@ -2467,7 +2467,7 @@
         <v>-11.0363</v>
       </c>
       <c r="N26" t="n">
-        <v>-9.0061</v>
+        <v>-9.006099999999998</v>
       </c>
       <c r="O26" t="n">
         <v>-2.0301</v>
@@ -2482,13 +2482,13 @@
         <v>15.6273</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.1871</v>
+        <v>-1.5131</v>
       </c>
       <c r="T26" t="n">
         <v>-0.9203999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.2669</v>
+        <v>-0.5928999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>7.476399999999999</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484259_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484259_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>G. PEREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,11 +964,16 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0708</v>
+        <v>0.614</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6173999999999999</v>
+        <v>0.614</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6882</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1383</v>
+        <v>0.614</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0617</v>
+        <v>0.614</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4858</v>
+        <v>0.614</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1461</v>
+        <v>0.614</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6603</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6241</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0844</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5397</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0138</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1265</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1402</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1016,12 +1046,17 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1068,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.147</v>
+        <v>0.0708</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9778</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1692</v>
+        <v>0.6882</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3981</v>
+        <v>-0.1383</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1267</v>
+        <v>1.0617</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7286</v>
+        <v>-1.2</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.4858</v>
       </c>
       <c r="K8" t="n">
-        <v>0.472</v>
+        <v>1.1461</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0809</v>
+        <v>-0.6603</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1548</v>
+        <v>-0.6241</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6546999999999999</v>
+        <v>-0.0844</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8095</v>
+        <v>-0.5397</v>
       </c>
       <c r="P8" t="n">
         <v>0.1953</v>
@@ -1078,28 +1113,33 @@
         <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4196</v>
+        <v>0.0138</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1102</v>
+        <v>-0.1265</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3094</v>
+        <v>0.1402</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.16</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. LLORCA CASTILLO</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4033</v>
+        <v>-1.147</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5169</v>
+        <v>-0.9778</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1136</v>
+        <v>-0.1692</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8083</v>
+        <v>0.3981</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5107</v>
+        <v>1.1267</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.319</v>
+        <v>-0.7286</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.113</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8007</v>
+        <v>0.472</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9137</v>
+        <v>0.0809</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3047</v>
+        <v>-0.1548</v>
       </c>
       <c r="N9" t="n">
-        <v>0.71</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4052</v>
+        <v>-0.8095</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1255</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0226</v>
+        <v>0.4196</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0514</v>
+        <v>0.1102</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0741</v>
+        <v>0.3094</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5545</v>
+        <v>-2.16</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7731</v>
+        <v>-0.6642</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>A. LLORCA CASTILLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2945</v>
+        <v>-1.4033</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4859</v>
+        <v>-2.5169</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1914</v>
+        <v>1.1136</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3824</v>
+        <v>-0.8083</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8836000000000001</v>
+        <v>1.5107</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4988</v>
+        <v>-2.319</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3077</v>
+        <v>-1.113</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6741</v>
+        <v>0.8007</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.9137</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0747</v>
+        <v>0.3047</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2095</v>
+        <v>0.71</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1348</v>
+        <v>-0.4052</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.586</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0488</v>
+        <v>0.0226</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2015</v>
+        <v>-0.0514</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1527</v>
+        <v>0.0741</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2772</v>
+        <v>0.5545</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3316</v>
+        <v>-2.2945</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2977</v>
+        <v>-2.4859</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0338</v>
+        <v>0.1914</v>
       </c>
       <c r="G11" t="n">
-        <v>1.024</v>
+        <v>-1.3824</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4237</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3997</v>
+        <v>-0.4988</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3</v>
+        <v>-1.3077</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2947</v>
+        <v>-0.6741</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9947</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7239</v>
+        <v>-0.0747</v>
       </c>
       <c r="N11" t="n">
-        <v>1.129</v>
+        <v>-0.2095</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4051</v>
+        <v>0.1348</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.9534</v>
+        <v>-0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.1255</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0351</v>
+        <v>-0.0488</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5276999999999999</v>
+        <v>-0.2015</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5074</v>
+        <v>0.1527</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4373</v>
+        <v>-0.2772</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4373</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0059</v>
+        <v>-2.9455</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4855</v>
+        <v>-2.9117</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5203</v>
+        <v>-0.0338</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5312</v>
+        <v>0.41</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7468</v>
+        <v>2.8097</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2156</v>
+        <v>-2.3997</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2468</v>
+        <v>-0.3139</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.3277</v>
+        <v>1.6807</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0809</v>
+        <v>-1.9947</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2844</v>
+        <v>0.7239</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.419</v>
+        <v>1.129</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1346</v>
+        <v>-0.4051</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3907</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R12" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1974</v>
+        <v>1.0351</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.262</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0646</v>
+        <v>0.5074</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8865</v>
+        <v>-2.4373</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8865</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.432</v>
+        <v>-3.0059</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2426</v>
+        <v>-2.4855</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1894</v>
+        <v>-0.5203</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.0556</v>
+        <v>-1.5312</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8667</v>
+        <v>-1.7468</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1889</v>
+        <v>0.2156</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1854</v>
+        <v>-1.2468</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.2663</v>
+        <v>-1.3277</v>
       </c>
       <c r="L13" t="n">
         <v>0.0809</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1298</v>
+        <v>-0.2844</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3996</v>
+        <v>-0.419</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2698</v>
+        <v>0.1346</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4079</v>
+        <v>-0.1974</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0805</v>
+        <v>-0.262</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3275</v>
+        <v>0.0646</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.7731</v>
+        <v>-0.8865</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7731</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,379 +1566,400 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.244299999999999</v>
+        <v>-3.432</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4651</v>
+        <v>-2.2426</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7793</v>
+        <v>-1.1894</v>
       </c>
       <c r="G14" t="n">
-        <v>13.1844</v>
+        <v>-1.0556</v>
       </c>
       <c r="H14" t="n">
-        <v>13.8556</v>
+        <v>-0.8667</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6712000000000007</v>
+        <v>-0.1889</v>
       </c>
       <c r="J14" t="n">
-        <v>11.0363</v>
+        <v>-1.1854</v>
       </c>
       <c r="K14" t="n">
-        <v>9.006200000000002</v>
+        <v>-1.2663</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0301</v>
+        <v>0.0809</v>
       </c>
       <c r="M14" t="n">
-        <v>2.148</v>
+        <v>0.1298</v>
       </c>
       <c r="N14" t="n">
-        <v>4.849500000000001</v>
+        <v>0.3996</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.701300000000001</v>
+        <v>-0.2698</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.9535</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>-15.6273</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>13.6741</v>
+        <v>0.7814</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4898</v>
+        <v>-0.4079</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5694</v>
+        <v>-0.0805</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9202</v>
+        <v>-0.3275</v>
       </c>
       <c r="V14" t="n">
-        <v>-7.476100000000001</v>
+        <v>-1.7731</v>
       </c>
       <c r="W14" t="n">
-        <v>5.4868</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-12.963</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7003</v>
+        <v>6.244400000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9192</v>
+        <v>2.465100000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7811</v>
+        <v>3.7793</v>
       </c>
       <c r="G15" t="n">
-        <v>0.067</v>
+        <v>13.1844</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.526</v>
+        <v>13.8556</v>
       </c>
       <c r="I15" t="n">
-        <v>0.593</v>
+        <v>-0.6712000000000007</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5803</v>
+        <v>11.0364</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3121</v>
+        <v>9.0062</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2683</v>
+        <v>2.030099999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5133</v>
+        <v>2.148</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.838</v>
+        <v>4.849500000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6753</v>
+        <v>-2.7013</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>-1.9535</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1488</v>
+        <v>-15.6273</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7348</v>
+        <v>13.6741</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.39</v>
+        <v>2.4898</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0504</v>
+        <v>1.5694</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4404</v>
+        <v>0.9202</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4373</v>
+        <v>-7.476099999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4373</v>
+        <v>5.486800000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
-      </c>
+        <v>-12.963</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7712</v>
+        <v>2.3933</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9338</v>
+        <v>1.6122</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7051</v>
+        <v>0.7811</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6052</v>
+        <v>-0.24</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9992</v>
+        <v>-0.833</v>
       </c>
       <c r="I16" t="n">
-        <v>0.606</v>
+        <v>0.593</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1095</v>
+        <v>1.2733</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9071</v>
+        <v>0.0051</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2023</v>
+        <v>1.2683</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5042</v>
+        <v>-1.5133</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9079</v>
+        <v>-0.838</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4037</v>
+        <v>-0.6753</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.1488</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3441</v>
+        <v>2.7348</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.52</v>
+        <v>-0.39</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5624</v>
+        <v>0.0504</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0425</v>
+        <v>-0.4404</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5094</v>
+        <v>2.4373</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3321</v>
+        <v>2.4373</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1773</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4811</v>
+        <v>0.7712</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7943</v>
+        <v>-0.9338</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2754</v>
+        <v>1.7051</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4781</v>
+        <v>1.6052</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3431</v>
+        <v>0.9992</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.135</v>
+        <v>0.606</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6127</v>
+        <v>2.1095</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6127</v>
+        <v>1.9071</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.2023</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1346</v>
+        <v>-0.5042</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2696</v>
+        <v>-0.9079</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.135</v>
+        <v>0.4037</v>
       </c>
       <c r="P17" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R17" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0138</v>
+        <v>-0.52</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1816</v>
+        <v>-0.5624</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1678</v>
+        <v>0.0425</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3869</v>
+        <v>-0.5094</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3869</v>
+        <v>-0.1773</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>J. BERTOMEU BALDE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0814</v>
+        <v>0.4811</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2873</v>
+        <v>-0.7943</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3687</v>
+        <v>1.2754</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.1981</v>
+        <v>-0.4781</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.2512</v>
+        <v>-0.3431</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0531</v>
+        <v>-0.135</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1988</v>
+        <v>-0.6127</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5296</v>
+        <v>-0.6127</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7284</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3969</v>
+        <v>0.1346</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7217</v>
+        <v>0.2696</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6753</v>
+        <v>-0.135</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3535</v>
+        <v>-0.0138</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2736</v>
+        <v>-0.1816</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0799</v>
+        <v>0.1678</v>
       </c>
       <c r="V18" t="n">
-        <v>4.033</v>
+        <v>0.3869</v>
       </c>
       <c r="W18" t="n">
-        <v>4.4876</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4545</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1884,621 +1970,906 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2096</v>
+        <v>0.307</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5666</v>
+        <v>0.307</v>
       </c>
       <c r="F19" t="n">
-        <v>2.357</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.484</v>
+        <v>0.307</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8921</v>
+        <v>0.307</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.592</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.7146</v>
+        <v>0.307</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5283</v>
+        <v>0.307</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1863</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7694</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3638</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4056</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7348</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1479</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1247</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2726</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6836</v>
+        <v>0.307</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1438</v>
+        <v>0.307</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8274</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8363</v>
+        <v>0.307</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7153</v>
+        <v>0.307</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.121</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1373</v>
+        <v>0.307</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0169</v>
+        <v>0.307</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1204</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.699</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6984</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3514</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1794</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1721</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9738</v>
+        <v>-0.0814</v>
       </c>
       <c r="E21" t="n">
-        <v>0.324</v>
+        <v>1.2873</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2978</v>
+        <v>-1.3687</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0508</v>
+        <v>-2.1981</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9153</v>
+        <v>-2.2512</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1354</v>
+        <v>0.0531</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6127</v>
+        <v>0.1988</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6127</v>
+        <v>-0.5296</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.7284</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.438</v>
+        <v>-2.3969</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3026</v>
+        <v>-1.7217</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1354</v>
+        <v>-0.6753</v>
       </c>
       <c r="P21" t="n">
-        <v>0.586</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.1255</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7277</v>
+        <v>-0.3535</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.282</v>
+        <v>-0.2736</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4458</v>
+        <v>-0.0799</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2186</v>
+        <v>4.033</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>4.4876</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.4545</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. GONZÁLEZ BRUMOS</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3811</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.355</v>
+        <v>-2.8736</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0261</v>
+        <v>2.357</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.372</v>
+        <v>-2.791</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.6278</v>
+        <v>-1.199</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2558</v>
+        <v>-1.592</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7241</v>
+        <v>-2.0216</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3853</v>
+        <v>-0.8353</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6613</v>
+        <v>-1.1863</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.648</v>
+        <v>-0.7694</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2425</v>
+        <v>-0.3638</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4054</v>
+        <v>-0.4056</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7581</v>
+        <v>1.7581</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1255</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3674</v>
+        <v>2.7348</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2118</v>
+        <v>-0.1479</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.22</v>
+        <v>0.1247</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4318</v>
+        <v>-0.2726</v>
       </c>
       <c r="V22" t="n">
-        <v>2.5372</v>
+        <v>0.6642</v>
       </c>
       <c r="W22" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1773</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4364</v>
+        <v>-0.6836</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6522</v>
+        <v>0.1438</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7842</v>
+        <v>-0.8274</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.1937</v>
+        <v>-1.8363</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6526</v>
+        <v>-1.7153</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4589</v>
+        <v>-0.121</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1186</v>
+        <v>-1.1373</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.7128</v>
+        <v>-1.0169</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5942</v>
+        <v>-0.1204</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0751</v>
+        <v>-0.699</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0601</v>
+        <v>-0.6984</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1352</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8309</v>
+        <v>-0.3514</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6618000000000001</v>
+        <v>-0.1794</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1691</v>
+        <v>-0.1721</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.0503</v>
+        <v>0.3321</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.0503</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0128</v>
+        <v>-0.9738</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8853</v>
+        <v>0.324</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1275</v>
+        <v>-1.2978</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2619</v>
+        <v>-2.0508</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1267</v>
+        <v>-1.9153</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1352</v>
+        <v>-0.1354</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0985</v>
+        <v>-0.6127</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0985</v>
+        <v>-0.6127</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1634</v>
+        <v>-1.438</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0281</v>
+        <v>-1.3026</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1352</v>
+        <v>-0.1354</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2078</v>
+        <v>-0.7277</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1899</v>
+        <v>-0.282</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0178</v>
+        <v>-0.4458</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1773</v>
+        <v>1.2186</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1773</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>P. GONZALEZ BRUMOS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.4415</v>
+        <v>-1.3811</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2663</v>
+        <v>-1.355</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1752</v>
+        <v>-0.0261</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9816</v>
+        <v>-2.372</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.8046</v>
+        <v>-2.6278</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8229</v>
+        <v>0.2558</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0181</v>
+        <v>-0.7241</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.5718</v>
+        <v>-1.3853</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5537</v>
+        <v>0.6613</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9636</v>
+        <v>-1.648</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.2328</v>
+        <v>-1.2425</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2692</v>
+        <v>-0.4054</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1953</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-3.1255</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2593</v>
+        <v>0.2118</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2482</v>
+        <v>-0.22</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0111</v>
+        <v>0.4318</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.3959</v>
+        <v>2.5372</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.3959</v>
+        <v>-0.1773</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
+        <v>-1.4364</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.6522</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.7842</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.1937</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.6526</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.4589</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.1186</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.7128</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.5942</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.0751</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.0601</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.1352</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.8309</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.6618000000000001</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-2.0503</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-2.0503</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>J. LLORENTE GUILLEMI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-2.0128</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.8853</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.1275</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.2619</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.1267</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.1352</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.0985</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.0985</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1.1634</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1.0281</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.1352</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.2078</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.1899</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.1773</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.1773</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>G. LOZANO MASSANET</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-2.4415</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.2663</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-2.1752</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.9816</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1.8046</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8229</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.0181</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.5718</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.5537</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.9636</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-1.2328</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-0.2593</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.2482</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-1.3959</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-1.3959</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484259_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
         <v>-5.2676</v>
       </c>
-      <c r="E26" t="n">
-        <v>-3.7792</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-1.4883</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="E29" t="n">
+        <v>-3.779199999999999</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-1.488299999999999</v>
+      </c>
+      <c r="G29" t="n">
         <v>-13.1843</v>
       </c>
-      <c r="H26" t="n">
-        <v>-13.8555</v>
-      </c>
-      <c r="I26" t="n">
+      <c r="H29" t="n">
+        <v>-13.8554</v>
+      </c>
+      <c r="I29" t="n">
         <v>0.6710999999999997</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J29" t="n">
         <v>-2.148</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K29" t="n">
         <v>-4.849399999999999</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L29" t="n">
         <v>2.7015</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M29" t="n">
         <v>-11.0363</v>
       </c>
-      <c r="N26" t="n">
-        <v>-9.006099999999998</v>
-      </c>
-      <c r="O26" t="n">
+      <c r="N29" t="n">
+        <v>-9.0061</v>
+      </c>
+      <c r="O29" t="n">
         <v>-2.0301</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P29" t="n">
         <v>1.9533</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q29" t="n">
         <v>-13.674</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R29" t="n">
         <v>15.6273</v>
       </c>
-      <c r="S26" t="n">
-        <v>-1.5131</v>
-      </c>
-      <c r="T26" t="n">
+      <c r="S29" t="n">
+        <v>-1.513100000000001</v>
+      </c>
+      <c r="T29" t="n">
         <v>-0.9203999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U29" t="n">
         <v>-0.5928999999999999</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V29" t="n">
         <v>7.476399999999999</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W29" t="n">
         <v>12.9632</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X29" t="n">
         <v>-5.4867</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
